--- a/sources/num.xlsx
+++ b/sources/num.xlsx
@@ -2708,7 +2708,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>General Fimiston Site</t>
+          <t>General FIM Site</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Primary Crushing – Fimiston Existing</t>
+          <t>Primary Crushing – FIM Existing</t>
         </is>
       </c>
     </row>
